--- a/backend/data/Code_Mapping_Table.xlsx
+++ b/backend/data/Code_Mapping_Table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,83 +436,513 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Old Description</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>New Item Code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>New Description</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Reason for Change</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Effective Date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Reason</t>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Mapped By</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>OLD001</t>
+          <t>OLD-101</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ITEM001</t>
+          <t>M12 Bolt (legacy)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>ITM-1001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>System Update</t>
+          <t>Heavy Duty Steel Bolt M12</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Catalogue consolidation</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>System Admin</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>OLD002</t>
+          <t>OLD-102</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ITEM002</t>
+          <t>M12 Nut (legacy)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>ITM-1002</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>System Update</t>
+          <t>Stainless Steel Nut M12</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Catalogue consolidation</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>System Admin</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OLD003</t>
+          <t>OLD-LUB1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ITEM999</t>
+          <t>Lubricant 5L (v1)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>ITM-1003</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Industrial Lubricant 5L</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Supplier change</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>OLD-GLOV</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Work Gloves L</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ITM-1004</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Safety Gloves (L)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Safety standard update</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>HSE Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>OLD-PIPE1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PVC 50mm 3m</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ITM-1005</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PVC Pipe 50mm x 3m</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Spec update</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2023-11-01</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>OLD-CABLE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2.5mm Cable 100m</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ITM-1006</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Electrical Cable 2.5mm 100m</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Catalogue consolidation</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>System Admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>OLD-FLOOD</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>500W Halogen Flood</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ITM-1007</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LED Floodlight 50W</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Energy efficiency upgrade</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Discontinued</t>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CONC-MIX</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Concrete 25kg bag</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ITM-1008</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Concrete Mix 25kg</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Code format standardisation</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>System Admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PRMER-W</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>White Primer 10L</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ITM-1009</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Paint Primer White 10L</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Code format standardisation</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>System Admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ITM-2001</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Steel Washer M12</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ITM-1002</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stainless Steel Nut M12</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Superseded by ITM-1002 bundle</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ITM-2002</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Industrial Lubricant 1L (Old)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ITM-1003</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Industrial Lubricant 5L</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Bulk pack only</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ITM-2003</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Halogen Floodlight 500W</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ITM-1007</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LED Floodlight 50W</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Phase-out halogen</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ITM-2004</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PVC Pipe 50mm x 2m (Old Spec)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ITM-1005</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PVC Pipe 50mm x 3m</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Length standard changed</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2022-09-10</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
